--- a/work/data/leaderboard_text_coding.xlsx
+++ b/work/data/leaderboard_text_coding.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>claude-fable-5</t>
+          <t>claude-fable-5-high</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">

--- a/work/data/leaderboard_text_coding.xlsx
+++ b/work/data/leaderboard_text_coding.xlsx
@@ -47,17 +47,17 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="00D9D9D9"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="00FFD700"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Calibri"/>
       <color rgb="0000B050"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00D9D9D9"/>
       <sz val="8"/>
     </font>
     <font>
@@ -81,6 +81,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFD700"/>
         <bgColor rgb="00FFD700"/>
       </patternFill>
@@ -89,12 +95,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="0000B050"/>
         <bgColor rgb="0000B050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-        <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -540,11 +540,11 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>claude-fable-5-high</t>
+          <t>claude-opus-4-6-high</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1552</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="3" ht="11" customHeight="1">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1552</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="4" ht="11" customHeight="1">
@@ -570,7 +570,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-high</t>
+          <t>claude-fable-5-high</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
@@ -585,11 +585,11 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-4-7</t>
+          <t>claude-opus-4-6</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="6" ht="11" customHeight="1">
@@ -600,56 +600,56 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-4-6</t>
+          <t>claude-opus-5.5-high</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="7" ht="11" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="8" ht="11" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>mimo-v2.6-pro</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="9" ht="11" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
           <t>gpt-6-astra-max</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>1543</v>
-      </c>
-    </row>
-    <row r="8" ht="11" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>kimi-k3-max</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>1538</v>
-      </c>
-    </row>
-    <row r="9" ht="11" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>muse-spark-1.3-max</t>
-        </is>
-      </c>
       <c r="C9" s="4" t="n">
-        <v>1537</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="10" ht="11" customHeight="1">
@@ -660,41 +660,41 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
+          <t>kimi-k3-max</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="11" ht="11" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>muse-spark-1.3-max</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="12" ht="11" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
           <t>muse-spark-1.2 (xHigh)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
-        <v>1536</v>
-      </c>
-    </row>
-    <row r="11" ht="11" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>gemini-3.8-flash-high</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
+      <c r="C12" s="4" t="n">
         <v>1535</v>
-      </c>
-    </row>
-    <row r="12" ht="11" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>claude-opus-4-8-high</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>1533</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="1">
@@ -705,86 +705,86 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
+          <t>claude-opus-4-8-high</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="14" ht="11" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
           <t>claude-opus-5-high</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C14" s="4" t="n">
         <v>1533</v>
       </c>
     </row>
-    <row r="14" ht="11" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+    <row r="15" ht="11" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>muse-spark-1.1</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C15" s="4" t="n">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="16" ht="11" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>deepseek-v4.1-flash-max</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="17" ht="11" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>gemini-3.8-flash-high</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="18" ht="11" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>gpt-5.6-sol-xhigh</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
         <v>1531</v>
-      </c>
-    </row>
-    <row r="15" ht="11" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>claude-opus-4-5-20251101-high-32k</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>1530</v>
-      </c>
-    </row>
-    <row r="16" ht="11" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>claude-opus-4-8</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>1530</v>
-      </c>
-    </row>
-    <row r="17" ht="11" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-6</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>1528</v>
-      </c>
-    </row>
-    <row r="18" ht="11" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>gpt-5.6-sol-xhigh</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>1528</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="1">
@@ -795,71 +795,71 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-5-max</t>
+          <t>claude-opus-4-5-20251101-high-32k</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1526</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="21" ht="11" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
           <t>muse-spark</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n">
-        <v>1526</v>
-      </c>
-    </row>
-    <row r="21" ht="11" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>glm-5.3-flash</t>
-        </is>
-      </c>
       <c r="C21" s="4" t="n">
-        <v>1525</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>qwen3.7-max-preview</t>
+          <t>claude-fable-5.1-max</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1525</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>glm-5.3-max</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1524</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="1">
@@ -870,26 +870,26 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-4-5-20251101</t>
+          <t>claude-opus-5-max</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1523</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>qwen3.8-max</t>
+          <t>mimo-v2.6-flash</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1522</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="1">
@@ -900,11 +900,11 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>mimo-v2.5-pro</t>
+          <t>qwen3.7-max-preview</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1521</v>
+        <v>1525</v>
       </c>
     </row>
   </sheetData>

--- a/work/data/leaderboard_text_coding.xlsx
+++ b/work/data/leaderboard_text_coding.xlsx
@@ -32,7 +32,7 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="004472C4"/>
+      <color rgb="00FF0000"/>
       <sz val="8"/>
     </font>
     <font>
@@ -47,12 +47,7 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00D9D9D9"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00FFD700"/>
+      <color rgb="004472C4"/>
       <sz val="8"/>
     </font>
     <font>
@@ -62,7 +57,12 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00FF0000"/>
+      <color rgb="00D9D9D9"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00FFD700"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -75,8 +75,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+        <bgColor rgb="00FF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000B050"/>
+        <bgColor rgb="0000B050"/>
       </patternFill>
     </fill>
     <fill>
@@ -89,18 +101,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFD700"/>
         <bgColor rgb="00FFD700"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0000B050"/>
-        <bgColor rgb="0000B050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF0000"/>
-        <bgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -540,37 +540,37 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>gemini-4-argon-high</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="3" ht="11" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>claude-fable-5-high</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="4" ht="11" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
           <t>claude-opus-4-6-high</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>1551</v>
-      </c>
-    </row>
-    <row r="3" ht="11" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7-high</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>1551</v>
-      </c>
-    </row>
-    <row r="4" ht="11" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>claude-fable-5-high</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
@@ -578,29 +578,29 @@
       </c>
     </row>
     <row r="5" ht="11" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>claude-opus-4-7-high</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="6" ht="11" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
           <t>claude-opus-4-6</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>1548</v>
-      </c>
-    </row>
-    <row r="6" ht="11" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>claude-opus-5.5-high</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
@@ -608,7 +608,7 @@
       </c>
     </row>
     <row r="7" ht="11" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>■</t>
         </is>
@@ -623,52 +623,52 @@
       </c>
     </row>
     <row r="8" ht="11" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>kimi-k3-max</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="9" ht="11" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
           <t>mimo-v2.6-pro</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>1543</v>
-      </c>
-    </row>
-    <row r="9" ht="11" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="n">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="10" ht="11" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>gpt-6-astra-max</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n">
-        <v>1542</v>
-      </c>
-    </row>
-    <row r="10" ht="11" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>kimi-k3-max</t>
-        </is>
-      </c>
       <c r="C10" s="4" t="n">
-        <v>1541</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="11" ht="11" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>■</t>
         </is>
@@ -690,101 +690,101 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>claude-opus-5.5-high</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="13" ht="11" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>muse-spark-1.2 (xHigh)</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C13" s="4" t="n">
         <v>1535</v>
       </c>
     </row>
-    <row r="13" ht="11" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+    <row r="14" ht="11" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>muse-spark-1.1</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="15" ht="11" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>gpt-5.6-sol-xhigh</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="16" ht="11" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>claude-opus-5-high</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="17" ht="11" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>claude-opus-4-8-high</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n">
-        <v>1534</v>
-      </c>
-    </row>
-    <row r="14" ht="11" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>claude-opus-5-high</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
+      <c r="C17" s="4" t="n">
         <v>1533</v>
       </c>
     </row>
-    <row r="15" ht="11" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>muse-spark-1.1</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
+    <row r="18" ht="11" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>claude-fable-5.1-max</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
         <v>1532</v>
-      </c>
-    </row>
-    <row r="16" ht="11" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>deepseek-v4.1-flash-max</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>1532</v>
-      </c>
-    </row>
-    <row r="17" ht="11" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>gemini-3.8-flash-high</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>1532</v>
-      </c>
-    </row>
-    <row r="18" ht="11" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>gpt-5.6-sol-xhigh</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>1531</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="1">
@@ -795,7 +795,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-4-5-20251101-high-32k</t>
+          <t>gemini-3.8-flash-high</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
@@ -803,18 +803,18 @@
       </c>
     </row>
     <row r="20" ht="11" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-4-8</t>
+          <t>claude-opus-4-5-20251101-high-32k</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="1">
@@ -825,7 +825,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>muse-spark</t>
+          <t>claude-opus-4-8</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
@@ -833,44 +833,44 @@
       </c>
     </row>
     <row r="22" ht="11" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>claude-fable-5.1-max</t>
+          <t>claude-opus-5-max</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1529</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6</t>
+          <t>muse-spark</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1529</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-5-max</t>
+          <t>deepseek-v4.1-flash-max</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
@@ -885,15 +885,15 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>mimo-v2.6-flash</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1525</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>■</t>
         </is>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
   </sheetData>

--- a/work/data/leaderboard_text_coding.xlsx
+++ b/work/data/leaderboard_text_coding.xlsx
@@ -52,17 +52,17 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="00FFD700"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="0000B050"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Calibri"/>
       <color rgb="00D9D9D9"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00FFD700"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -87,6 +87,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFD700"/>
+        <bgColor rgb="00FFD700"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0000B050"/>
         <bgColor rgb="0000B050"/>
       </patternFill>
@@ -95,12 +101,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D9D9D9"/>
         <bgColor rgb="00D9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFD700"/>
-        <bgColor rgb="00FFD700"/>
       </patternFill>
     </fill>
   </fills>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1559</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="3" ht="11" customHeight="1">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="7" ht="11" customHeight="1">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1547</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="8" ht="11" customHeight="1">
@@ -630,105 +630,105 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>gpt-6-astra-max</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="9" ht="11" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>gpt-6.1-sol-max</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="10" ht="11" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
           <t>kimi-k3-max</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C10" s="4" t="n">
         <v>1541</v>
       </c>
     </row>
-    <row r="9" ht="11" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+    <row r="11" ht="11" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>mimo-v2.6-pro</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C11" s="4" t="n">
         <v>1540</v>
       </c>
     </row>
-    <row r="10" ht="11" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>gpt-6-astra-max</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
+    <row r="12" ht="11" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>muse-spark-1.3-max</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
         <v>1539</v>
       </c>
     </row>
-    <row r="11" ht="11" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>muse-spark-1.3-max</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>1539</v>
-      </c>
-    </row>
-    <row r="12" ht="11" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+    <row r="13" ht="11" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>claude-opus-5.5-high</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C13" s="4" t="n">
         <v>1538</v>
       </c>
     </row>
-    <row r="13" ht="11" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>muse-spark-1.2 (xHigh)</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>1535</v>
-      </c>
-    </row>
     <row r="14" ht="11" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>muse-spark-1.1</t>
+          <t>claude-sonnet-5.5-xhigh</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1534</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>■</t>
         </is>
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="1">
@@ -773,29 +773,29 @@
       </c>
     </row>
     <row r="18" ht="11" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>claude-fable-5.1-max</t>
+          <t>muse-spark-1.1</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1532</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>gemini-3.8-flash-high</t>
+          <t>muse-spark-1.2 (xHigh)</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
@@ -810,7 +810,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-4-5-20251101-high-32k</t>
+          <t>claude-fable-5.1-max</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
@@ -825,7 +825,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-4-8</t>
+          <t>claude-opus-4-5-20251101-high-32k</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
@@ -848,14 +848,14 @@
       </c>
     </row>
     <row r="23" ht="11" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>muse-spark</t>
+          <t>gemini-3.8-flash-high</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
@@ -863,48 +863,48 @@
       </c>
     </row>
     <row r="24" ht="11" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>deepseek-v4.1-flash-max</t>
+          <t>claude-opus-4-8</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="25" ht="11" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>muse-spark</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="26" ht="11" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
         <v>1529</v>
-      </c>
-    </row>
-    <row r="25" ht="11" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-6</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>1529</v>
-      </c>
-    </row>
-    <row r="26" ht="11" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>qwen3.7-max-preview</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>1524</v>
       </c>
     </row>
   </sheetData>

--- a/work/data/leaderboard_text_coding.xlsx
+++ b/work/data/leaderboard_text_coding.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1560</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="3" ht="11" customHeight="1">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1552</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="4" ht="11" customHeight="1">
@@ -570,11 +570,11 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-high</t>
+          <t>claude-opus-4-7-high</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="5" ht="11" customHeight="1">
@@ -585,11 +585,11 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-4-7-high</t>
+          <t>claude-opus-4-6-high</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="6" ht="11" customHeight="1">
@@ -600,11 +600,11 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-4-6</t>
+          <t>claude-opus-5.5-high</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1548</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="7" ht="11" customHeight="1">
@@ -615,26 +615,26 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="8" ht="11" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
           <t>claude-opus-4-7</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C8" s="4" t="n">
         <v>1546</v>
-      </c>
-    </row>
-    <row r="8" ht="11" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>gpt-6-astra-max</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>1543</v>
       </c>
     </row>
     <row r="9" ht="11" customHeight="1">
@@ -649,33 +649,33 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="10" ht="11" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>gpt-6-astra-max</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
         <v>1542</v>
       </c>
     </row>
-    <row r="10" ht="11" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+    <row r="11" ht="11" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>kimi-k3-max</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>1541</v>
-      </c>
-    </row>
-    <row r="11" ht="11" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>mimo-v2.6-pro</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
@@ -690,7 +690,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>muse-spark-1.3-max</t>
+          <t>mimo-v2.6-pro</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
@@ -698,14 +698,14 @@
       </c>
     </row>
     <row r="13" ht="11" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-5.5-high</t>
+          <t>muse-spark-1.3-max</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
@@ -713,29 +713,29 @@
       </c>
     </row>
     <row r="14" ht="11" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>claude-sonnet-5.5-xhigh</t>
+          <t>gpt-5.6-sol-xhigh</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>gpt-5.6-sol-xhigh</t>
+          <t>claude-opus-5-high</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
@@ -750,11 +750,11 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-5-high</t>
+          <t>claude-fable-5.1-max</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1533</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="1">
@@ -788,29 +788,29 @@
       </c>
     </row>
     <row r="19" ht="11" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
+          <t>claude-sonnet-5.5-xhigh</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="20" ht="11" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
           <t>muse-spark-1.2 (xHigh)</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>1531</v>
-      </c>
-    </row>
-    <row r="20" ht="11" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>claude-fable-5.1-max</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
@@ -829,18 +829,18 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-5-max</t>
+          <t>gemini-3.8-flash-high</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
@@ -848,14 +848,14 @@
       </c>
     </row>
     <row r="23" ht="11" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>gemini-3.8-flash-high</t>
+          <t>claude-opus-5-max</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="1">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="1">
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1529</v>
+        <v>1528</v>
       </c>
     </row>
   </sheetData>

--- a/work/data/leaderboard_text_coding.xlsx
+++ b/work/data/leaderboard_text_coding.xlsx
@@ -47,6 +47,11 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="00D9D9D9"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="004472C4"/>
       <sz val="8"/>
     </font>
@@ -58,11 +63,6 @@
     <font>
       <name val="Calibri"/>
       <color rgb="0000B050"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00D9D9D9"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -81,6 +81,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
       </patternFill>
@@ -95,12 +101,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="0000B050"/>
         <bgColor rgb="0000B050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-        <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1562</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="3" ht="11" customHeight="1">
@@ -555,37 +555,37 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>muse-wonder-max</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="4" ht="11" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
           <t>claude-fable-5-high</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C4" s="4" t="n">
         <v>1551</v>
       </c>
     </row>
-    <row r="4" ht="11" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+    <row r="5" ht="11" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>claude-opus-4-7-high</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>1550</v>
-      </c>
-    </row>
-    <row r="5" ht="11" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>claude-opus-4-6-high</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
@@ -593,22 +593,22 @@
       </c>
     </row>
     <row r="6" ht="11" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-5.5-high</t>
+          <t>claude-opus-4-6-high</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1550</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="7" ht="11" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>■</t>
         </is>
@@ -623,7 +623,7 @@
       </c>
     </row>
     <row r="8" ht="11" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>■</t>
         </is>
@@ -645,7 +645,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>gpt-6.1-sol-max</t>
+          <t>claude-opus-5.5-high</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
@@ -653,7 +653,7 @@
       </c>
     </row>
     <row r="10" ht="11" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>■</t>
         </is>
@@ -664,11 +664,11 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="11" ht="11" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>■</t>
         </is>
@@ -679,33 +679,33 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>mimo-v2.6-pro</t>
+          <t>muse-spark-1.2 (xHigh)</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1539</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>muse-spark-1.3-max</t>
+          <t>gpt-6.1-sol-max</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
@@ -713,18 +713,18 @@
       </c>
     </row>
     <row r="14" ht="11" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>gpt-5.6-sol-xhigh</t>
+          <t>mimo-v2.6-pro</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1535</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="1">
@@ -735,52 +735,52 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-5-high</t>
+          <t>muse-spark-1.3-max</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="16" ht="11" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>claude-fable-5.1-max</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="17" ht="11" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>gpt-5.6-sol-xhigh</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
         <v>1534</v>
       </c>
     </row>
-    <row r="16" ht="11" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>claude-fable-5.1-max</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>1534</v>
-      </c>
-    </row>
-    <row r="17" ht="11" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+    <row r="18" ht="11" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>claude-opus-4-8-high</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>1533</v>
-      </c>
-    </row>
-    <row r="18" ht="11" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>muse-spark-1.1</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
@@ -795,30 +795,30 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>claude-sonnet-5.5-xhigh</t>
+          <t>muse-spark-1.1</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1532</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>muse-spark-1.2 (xHigh)</t>
+          <t>claude-opus-5-high</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1531</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>■</t>
         </is>
@@ -833,33 +833,33 @@
       </c>
     </row>
     <row r="22" ht="11" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>gemini-3.8-flash-high</t>
+          <t>claude-opus-5-max</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-5-max</t>
+          <t>claude-opus-4-8</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="1">
@@ -870,7 +870,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>claude-opus-4-8</t>
+          <t>muse-spark</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
@@ -878,33 +878,33 @@
       </c>
     </row>
     <row r="25" ht="11" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>muse-spark</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1529</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6</t>
+          <t>gemini-3.8-flash-high</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
   </sheetData>
